--- a/Book1v2.xlsx
+++ b/Book1v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feder\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Giulio\Desktop\programmazione\html\Bingo\Speedrun Bingo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EA2D23-E007-4114-B552-F9A5E9EF8944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B2B42420-151A-4F01-A50C-37D722861B13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{B2B42420-151A-4F01-A50C-37D722861B13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -895,10 +895,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="2" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="3" builtinId="32"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="20% - Colore 1" xfId="1" builtinId="30"/>
+    <cellStyle name="40% - Colore 1" xfId="2" builtinId="31"/>
+    <cellStyle name="60% - Colore 1" xfId="3" builtinId="32"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -914,9 +914,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -954,7 +954,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1060,7 +1060,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1202,7 +1202,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1211,34 +1211,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14DAE213-D33B-4125-AFAD-43E17EBF59E3}">
   <dimension ref="A1:Z48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="14.21875" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" customWidth="1"/>
-    <col min="10" max="10" width="15.21875" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
-    <col min="15" max="15" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.109375" customWidth="1"/>
-    <col min="17" max="17" width="19.5546875" customWidth="1"/>
-    <col min="18" max="18" width="10.21875" customWidth="1"/>
-    <col min="19" max="19" width="12.77734375" customWidth="1"/>
-    <col min="20" max="20" width="15.5546875" customWidth="1"/>
-    <col min="21" max="21" width="11.33203125" customWidth="1"/>
-    <col min="22" max="22" width="17.109375" customWidth="1"/>
-    <col min="23" max="23" width="14.77734375" customWidth="1"/>
-    <col min="24" max="24" width="17.21875" customWidth="1"/>
-    <col min="26" max="26" width="23.77734375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" customWidth="1"/>
+    <col min="17" max="17" width="19.5703125" customWidth="1"/>
+    <col min="18" max="18" width="10.28515625" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" customWidth="1"/>
+    <col min="21" max="21" width="11.28515625" customWidth="1"/>
+    <col min="22" max="22" width="17.140625" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" customWidth="1"/>
+    <col min="24" max="24" width="17.28515625" customWidth="1"/>
+    <col min="26" max="26" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="15" t="s">
         <v>49</v>
@@ -1390,7 +1390,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="15" t="s">
         <v>101</v>
@@ -1460,7 +1460,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="15" t="s">
         <v>163</v>
@@ -1518,7 +1518,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="15" t="s">
         <v>120</v>
@@ -1564,7 +1564,7 @@
       <c r="Y5" s="5"/>
       <c r="Z5" s="5"/>
     </row>
-    <row r="6" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="15" t="s">
         <v>164</v>
@@ -1602,7 +1602,7 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -1636,7 +1636,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1664,7 +1664,7 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1692,7 +1692,7 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1720,7 +1720,7 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1748,7 +1748,7 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1776,7 +1776,7 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1804,7 +1804,7 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1832,7 +1832,7 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1860,7 +1860,7 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1888,7 +1888,7 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>1</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="15" t="s">
         <v>102</v>
@@ -2034,7 +2034,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="15" t="s">
         <v>124</v>
@@ -2094,7 +2094,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="15" t="s">
         <v>125</v>
@@ -2142,7 +2142,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="15" t="s">
         <v>148</v>
@@ -2184,7 +2184,7 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="15" t="s">
         <v>175</v>
@@ -2218,7 +2218,7 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
@@ -2250,7 +2250,7 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2278,7 +2278,7 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2306,7 +2306,7 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2334,7 +2334,7 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2362,7 +2362,7 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2390,7 +2390,7 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2418,7 +2418,7 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2446,7 +2446,7 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2474,7 +2474,7 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2502,7 +2502,7 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>2</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="15" t="s">
         <v>169</v>
@@ -2634,7 +2634,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="15" t="s">
         <v>170</v>
@@ -2676,7 +2676,7 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="15" t="s">
         <v>178</v>
@@ -2710,7 +2710,7 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2740,7 +2740,7 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2770,7 +2770,7 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2798,7 +2798,7 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2826,7 +2826,7 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2854,7 +2854,7 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2882,7 +2882,7 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2910,7 +2910,7 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="13"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2938,7 +2938,7 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="13"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2966,7 +2966,7 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="13"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2994,7 +2994,7 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="13"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3022,7 +3022,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="13"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
